--- a/tests/Stations tbv Mailchimp.xlsx
+++ b/tests/Stations tbv Mailchimp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hldeb\PycharmProjects\dashboard_meet_je_stad\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E21EF8EC-4553-4F5F-8109-C33863635766}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6F829F4-7E9E-4D63-9E6E-1643688E071F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{F22B4D03-44CC-4007-BD03-E349FDF24518}"/>
   </bookViews>
@@ -50,7 +50,7 @@
     <t>Fijnstof</t>
   </si>
   <si>
-    <t>test@test.com</t>
+    <t>test22@test22.com</t>
   </si>
 </sst>
 </file>
@@ -449,7 +449,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2">
-        <v>152</v>
+        <v>840</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>3</v>

--- a/tests/Stations tbv Mailchimp.xlsx
+++ b/tests/Stations tbv Mailchimp.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hldeb\PycharmProjects\dashboard_meet_je_stad\tests\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hldeb\PycharmProjects\meet_je_stad_utrecht\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6F829F4-7E9E-4D63-9E6E-1643688E071F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E12F4FD-2520-41FD-9EEE-E29A91837814}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{F22B4D03-44CC-4007-BD03-E349FDF24518}"/>
   </bookViews>
@@ -449,7 +449,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2">
-        <v>840</v>
+        <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>3</v>
